--- a/src/rodos_corpus/data/corpus/rendered/finance/FIN-REESTR-EDO-DOG-2026.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/finance/FIN-REESTR-EDO-DOG-2026.xlsx
@@ -424,17 +424,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,25 +463,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Сумма договора, ₽</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Подписант</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Канал</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Бумажный экземпляр</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Проверка контрагента</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Повторная проверка до</t>
         </is>
@@ -489,166 +495,233 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ТСУ-2027/01</t>
+          <t>РМ-2025/01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ООО «ТехСнаб-Урал»</t>
+          <t>АО «Редмаш»</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>20.01.2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Коммерческий директор</t>
+          <t>8 200 000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Генеральный директор</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>ЭДО</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>не оформляется, п. 6.2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>24.09.2026 пройдена</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>13.04.2026 пройдена</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13.04.2027</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>РМ-2027/01</t>
+          <t>KMP-2025/02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>АО «Редмаш»</t>
+          <t>ТОО «KazMashParts»</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>30.01.2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>6 800 000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Генеральный директор</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ЭДО</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>не оформляется, п. 6.2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>13.04.2026 пройдена</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>13.04.2027</t>
+          <t>22.01.2026 пройдена</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22.01.2027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>МТЦ-2025/10</t>
+          <t>ПНН-2025/08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ООО «Машторг-Центр»</t>
+          <t>ООО «Привод-НН»</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14.10.2025</t>
+          <t>11.03.2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>4 900 000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Коммерческий директор</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ЭДО</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>не оформляется, п. 6.2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>20.10.2025 пройдена</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>05.03.2026 пройдена</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>05.03.2027</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>МТЦ-2025/10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ООО «Машторг-Центр»</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19.05.2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3 800 000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Коммерческий директор</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ЭДО</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>не оформляется, п. 6.2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12.05.2026 пройдена</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12.05.2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>РСУ-2024/33</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ООО «Ремсервис-Урал»</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>04.11.2024</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>05.11.2024</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1 450 000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Коммерческий директор</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>ЭДО</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>не оформляется, п. 6.2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>11.11.2025 пройдена</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>11.11.2026</t>
         </is>
